--- a/docs/Mapping_casi_uso/3_dec_use_case.xlsx
+++ b/docs/Mapping_casi_uso/3_dec_use_case.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="722">
   <si>
     <t>ID USECASE</t>
   </si>
@@ -890,6 +890,12 @@
     <t>Rico_010</t>
   </si>
   <si>
+    <t>12222401</t>
+  </si>
+  <si>
+    <t>Rico_022</t>
+  </si>
+  <si>
     <t>12224123</t>
   </si>
   <si>
@@ -1154,6 +1160,12 @@
     <t>Trascr_026</t>
   </si>
   <si>
+    <t>1368</t>
+  </si>
+  <si>
+    <t>Trascr_039</t>
+  </si>
+  <si>
     <t>1381</t>
   </si>
   <si>
@@ -2106,6 +2118,12 @@
   </si>
   <si>
     <t>Citt_032</t>
+  </si>
+  <si>
+    <t>52332</t>
+  </si>
+  <si>
+    <t>Citt_055</t>
   </si>
   <si>
     <t>52341</t>
@@ -2218,7 +2236,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C358"/>
+  <dimension ref="A1:C361"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="11.68359375" customWidth="true" bestFit="true"/>
@@ -5089,6 +5107,30 @@
         <v>715</v>
       </c>
     </row>
+    <row r="359">
+      <c r="A359" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="B359" s="2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="B360" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="B361" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/docs/Mapping_casi_uso/3_dec_use_case.xlsx
+++ b/docs/Mapping_casi_uso/3_dec_use_case.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="732">
   <si>
     <t>ID USECASE</t>
   </si>
@@ -1970,6 +1970,12 @@
     <t>Citt_008</t>
   </si>
   <si>
+    <t>52115</t>
+  </si>
+  <si>
+    <t>Citt_057</t>
+  </si>
+  <si>
     <t>52121</t>
   </si>
   <si>
@@ -2006,6 +2012,12 @@
     <t>Citt_004</t>
   </si>
   <si>
+    <t>52144</t>
+  </si>
+  <si>
+    <t>Citt_056</t>
+  </si>
+  <si>
     <t>52153</t>
   </si>
   <si>
@@ -2030,6 +2042,12 @@
     <t>Citt_053</t>
   </si>
   <si>
+    <t>52157</t>
+  </si>
+  <si>
+    <t>Citt_054</t>
+  </si>
+  <si>
     <t>52211</t>
   </si>
   <si>
@@ -2130,6 +2148,18 @@
   </si>
   <si>
     <t>Citt_035</t>
+  </si>
+  <si>
+    <t>52711</t>
+  </si>
+  <si>
+    <t>Citt_058</t>
+  </si>
+  <si>
+    <t>52712</t>
+  </si>
+  <si>
+    <t>Citt_059</t>
   </si>
   <si>
     <t>52821</t>
@@ -2236,7 +2266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C361"/>
+  <dimension ref="A1:C366"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="11.68359375" customWidth="true" bestFit="true"/>
@@ -5131,6 +5161,46 @@
         <v>721</v>
       </c>
     </row>
+    <row r="362">
+      <c r="A362" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="B362" s="2" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="B363" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="B365" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>731</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/docs/Mapping_casi_uso/3_dec_use_case.xlsx
+++ b/docs/Mapping_casi_uso/3_dec_use_case.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="736">
   <si>
     <t>ID USECASE</t>
   </si>
@@ -1232,6 +1232,12 @@
     <t>Dic_Nasc_998_8</t>
   </si>
   <si>
+    <t>14880000</t>
+  </si>
+  <si>
+    <t>Dic_Nasc_998_9</t>
+  </si>
+  <si>
     <t>14950000</t>
   </si>
   <si>
@@ -1326,6 +1332,12 @@
   </si>
   <si>
     <t>Morte_018</t>
+  </si>
+  <si>
+    <t>2216</t>
+  </si>
+  <si>
+    <t>Morte_020</t>
   </si>
   <si>
     <t>2221</t>
@@ -2266,7 +2278,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C366"/>
+  <dimension ref="A1:C368"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="11.68359375" customWidth="true" bestFit="true"/>
@@ -5201,6 +5213,22 @@
         <v>731</v>
       </c>
     </row>
+    <row r="367">
+      <c r="A367" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="B368" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/docs/Mapping_casi_uso/3_dec_use_case.xlsx
+++ b/docs/Mapping_casi_uso/3_dec_use_case.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="744">
   <si>
     <t>ID USECASE</t>
   </si>
@@ -1622,6 +1622,12 @@
     <t>Matr_Riconc_999</t>
   </si>
   <si>
+    <t>364000</t>
+  </si>
+  <si>
+    <t>Matr_999_3</t>
+  </si>
+  <si>
     <t>365699</t>
   </si>
   <si>
@@ -1736,6 +1742,12 @@
     <t>Trascr_UnCiv_005</t>
   </si>
   <si>
+    <t>438100</t>
+  </si>
+  <si>
+    <t>Trascr_UnCiv_006</t>
+  </si>
+  <si>
     <t>439999</t>
   </si>
   <si>
@@ -1838,6 +1850,12 @@
     <t>UnCiv_998_5</t>
   </si>
   <si>
+    <t>461000</t>
+  </si>
+  <si>
+    <t>UnCiv_009</t>
+  </si>
+  <si>
     <t>50000000</t>
   </si>
   <si>
@@ -2058,6 +2076,12 @@
   </si>
   <si>
     <t>Citt_054</t>
+  </si>
+  <si>
+    <t>52158</t>
+  </si>
+  <si>
+    <t>Citt_060</t>
   </si>
   <si>
     <t>52211</t>
@@ -2278,7 +2302,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C368"/>
+  <dimension ref="A1:C372"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="11.68359375" customWidth="true" bestFit="true"/>
@@ -5229,6 +5253,38 @@
         <v>735</v>
       </c>
     </row>
+    <row r="369">
+      <c r="A369" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="B369" s="2" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="B370" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="B371" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="B372" s="2" t="s">
+        <v>743</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
